--- a/public/downloads/Sainifirst2023.xlsx
+++ b/public/downloads/Sainifirst2023.xlsx
@@ -8,20 +8,22 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="MATLANTISv8" sheetId="8" r:id="rId8"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="52">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -53,10 +55,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -131,6 +133,27 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>Ru</t>
   </si>
   <si>
@@ -152,10 +175,10 @@
     <t>CO</t>
   </si>
   <si>
-    <t>NO</t>
+    <t>H</t>
   </si>
   <si>
-    <t>H</t>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -641,10 +664,10 @@
         <v>2347</v>
       </c>
       <c r="N3" s="5">
-        <v>5445.748450517654</v>
+        <v>5445748.450517654</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03315443429394507</v>
+        <v>33.15443429394507</v>
       </c>
       <c r="P3" s="5">
         <v>164254</v>
@@ -691,10 +714,10 @@
         <v>2347</v>
       </c>
       <c r="N4" s="5">
-        <v>33470.09135270119</v>
+        <v>33470091.35270119</v>
       </c>
       <c r="O4" s="4">
-        <v>0.08231983234223803</v>
+        <v>82.31983234223803</v>
       </c>
       <c r="P4" s="5">
         <v>406586</v>
@@ -741,10 +764,10 @@
         <v>2347</v>
       </c>
       <c r="N5" s="5">
-        <v>23524.47955107689</v>
+        <v>23524479.55107689</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1311864173804345</v>
+        <v>131.1864173804344</v>
       </c>
       <c r="P5" s="5">
         <v>179321</v>
@@ -791,10 +814,10 @@
         <v>2347</v>
       </c>
       <c r="N6" s="5">
-        <v>52611.6980483532</v>
+        <v>52611698.0483532</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08874159680525921</v>
+        <v>88.74159680525921</v>
       </c>
       <c r="P6" s="5">
         <v>592864</v>
@@ -841,10 +864,10 @@
         <v>450</v>
       </c>
       <c r="N7" s="5">
-        <v>6814.413580417633</v>
+        <v>6814413.580417633</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2907421102661333</v>
+        <v>290.7421102661334</v>
       </c>
       <c r="P7" s="5">
         <v>23438</v>
@@ -891,10 +914,10 @@
         <v>2347</v>
       </c>
       <c r="N8" s="5">
-        <v>26192.34820961952</v>
+        <v>26192348.20961952</v>
       </c>
       <c r="O8" s="4">
-        <v>0.1468938477781116</v>
+        <v>146.8938477781116</v>
       </c>
       <c r="P8" s="5">
         <v>178308</v>
@@ -920,7 +943,1068 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1208029301225156</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1164357392225056</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1008677856782264</v>
+      </c>
+      <c r="E3" s="4">
+        <v>93.33767361111113</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.10437639821068</v>
+      </c>
+      <c r="G3" s="5">
+        <v>768</v>
+      </c>
+      <c r="H3" s="5">
+        <v>762</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.04944611452185842</v>
+      </c>
+      <c r="O3" s="5">
+        <v>762</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1191112156310864</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1151200436289538</v>
+      </c>
+      <c r="R3" s="5">
+        <v>762</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6726984132912174</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.6750157754981174</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.7014459875671282</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.2354409464044</v>
+      </c>
+      <c r="F4" s="4">
+        <v>91.12934926498252</v>
+      </c>
+      <c r="G4" s="5">
+        <v>387</v>
+      </c>
+      <c r="H4" s="5">
+        <v>384</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.6750157754981174</v>
+      </c>
+      <c r="O4" s="5">
+        <v>384</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07133916625296793</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06956103689017767</v>
+      </c>
+      <c r="R4" s="5">
+        <v>384</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.743969930403469</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.7470720611733199</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.7830508365590264</v>
+      </c>
+      <c r="E5" s="4">
+        <v>94.83978041618792</v>
+      </c>
+      <c r="F5" s="4">
+        <v>94.68215268906204</v>
+      </c>
+      <c r="G5" s="5">
+        <v>373</v>
+      </c>
+      <c r="H5" s="5">
+        <v>370</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.7470720611733199</v>
+      </c>
+      <c r="O5" s="5">
+        <v>370</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1174712148105223</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1152964009382985</v>
+      </c>
+      <c r="R5" s="5">
+        <v>370</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.4001593216554759</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.4001593216554759</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.4312794525629082</v>
+      </c>
+      <c r="E6" s="4">
+        <v>94.36210549793688</v>
+      </c>
+      <c r="F6" s="4">
+        <v>94.49636923753988</v>
+      </c>
+      <c r="G6" s="5">
+        <v>366</v>
+      </c>
+      <c r="H6" s="5">
+        <v>366</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-0.3985188860917027</v>
+      </c>
+      <c r="O6" s="5">
+        <v>366</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1039660288404617</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1039660288404617</v>
+      </c>
+      <c r="R6" s="5">
+        <v>366</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.6602296127143477</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.6632745647065104</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.6900633889062732</v>
+      </c>
+      <c r="E7" s="4">
+        <v>89.95468019610078</v>
+      </c>
+      <c r="F7" s="4">
+        <v>91.34824965942781</v>
+      </c>
+      <c r="G7" s="5">
+        <v>358</v>
+      </c>
+      <c r="H7" s="5">
+        <v>355</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>-0.6632745647065104</v>
+      </c>
+      <c r="O7" s="5">
+        <v>355</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.08896950673792484</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.08605916275446153</v>
+      </c>
+      <c r="R7" s="5">
+        <v>355</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1.233992995803142</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.1693688893909946</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.0818765785737585</v>
+      </c>
+      <c r="E8" s="4">
+        <v>85.03401360544217</v>
+      </c>
+      <c r="F8" s="4">
+        <v>55.56224503224157</v>
+      </c>
+      <c r="G8" s="5">
+        <v>34</v>
+      </c>
+      <c r="H8" s="5">
+        <v>5</v>
+      </c>
+      <c r="I8" s="5">
+        <v>21</v>
+      </c>
+      <c r="J8" s="5">
+        <v>8</v>
+      </c>
+      <c r="K8" s="5">
+        <v>8</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>-0.1693688893909946</v>
+      </c>
+      <c r="O8" s="5">
+        <v>5</v>
+      </c>
+      <c r="P8" s="4">
+        <v>1.080621056438547</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.06158696927266263</v>
+      </c>
+      <c r="R8" s="5">
+        <v>5</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.5273506053844588</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.5273506053844588</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.3549032685483309</v>
+      </c>
+      <c r="E9" s="4">
+        <v>87.90594498669033</v>
+      </c>
+      <c r="F9" s="4">
+        <v>90.44013228285158</v>
+      </c>
+      <c r="G9" s="5">
+        <v>23</v>
+      </c>
+      <c r="H9" s="5">
+        <v>23</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4">
+        <v>-0.5273506053844588</v>
+      </c>
+      <c r="O9" s="5">
+        <v>23</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1176321160800899</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1176321160800899</v>
+      </c>
+      <c r="R9" s="5">
+        <v>23</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0.1069924771169251</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.1069924771169251</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.0293032420202812</v>
+      </c>
+      <c r="E10" s="4">
+        <v>87.18045112781958</v>
+      </c>
+      <c r="F10" s="4">
+        <v>90.08124337689878</v>
+      </c>
+      <c r="G10" s="5">
+        <v>19</v>
+      </c>
+      <c r="H10" s="5">
+        <v>19</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>-0.1069924771169251</v>
+      </c>
+      <c r="O10" s="5">
+        <v>19</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.08782386185518783</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.08782386185518783</v>
+      </c>
+      <c r="R10" s="5">
+        <v>19</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0.7082824204476088</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.7082824204476088</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.4929906137282688</v>
+      </c>
+      <c r="E11" s="4">
+        <v>86.96025778732547</v>
+      </c>
+      <c r="F11" s="4">
+        <v>88.50582832921232</v>
+      </c>
+      <c r="G11" s="5">
+        <v>19</v>
+      </c>
+      <c r="H11" s="5">
+        <v>19</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>-0.7082824204476088</v>
+      </c>
+      <c r="O11" s="5">
+        <v>19</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.06936836959631029</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.06936836959631029</v>
+      </c>
+      <c r="R11" s="5">
+        <v>19</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>97.91222837665104</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.065189603749467</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.022582019599489</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.2130379207498935</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.8095440988495952</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.1705260774251749</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1475769190290183</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1477748018957475</v>
+      </c>
+      <c r="K3" s="4">
+        <v>93.53269045155318</v>
+      </c>
+      <c r="L3" s="4">
+        <v>92.5822960245315</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2347</v>
+      </c>
+      <c r="N3" s="5">
+        <v>5445748.450517654</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.15443429394507</v>
+      </c>
+      <c r="P3" s="5">
+        <v>164254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>85.64124414145718</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.4686834256497656</v>
+      </c>
+      <c r="D4" s="3">
+        <v>13.89007243289305</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.5965061780997017</v>
+      </c>
+      <c r="F4" s="3">
+        <v>13.29356625479335</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.2276509485425082</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.182962384612822</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2132956707178462</v>
+      </c>
+      <c r="K4" s="4">
+        <v>84.52786738896678</v>
+      </c>
+      <c r="L4" s="4">
+        <v>84.19931580036024</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2347</v>
+      </c>
+      <c r="N4" s="5">
+        <v>33470091.35270119</v>
+      </c>
+      <c r="O4" s="4">
+        <v>82.31983234223803</v>
+      </c>
+      <c r="P4" s="5">
+        <v>406586</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>98.21048146570089</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.8947592671495527</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.8947592671495527</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.2556455048998722</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.6391137622496805</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1234661682467707</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1122311920904071</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1021687578544897</v>
+      </c>
+      <c r="K5" s="4">
+        <v>93.92240492277006</v>
+      </c>
+      <c r="L5" s="4">
+        <v>93.30413712969731</v>
+      </c>
+      <c r="M5" s="5">
+        <v>2347</v>
+      </c>
+      <c r="N5" s="5">
+        <v>23524479.55107689</v>
+      </c>
+      <c r="O5" s="4">
+        <v>131.1864173804344</v>
+      </c>
+      <c r="P5" s="5">
+        <v>179321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>83.29782701320835</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.150404772049425</v>
+      </c>
+      <c r="D6" s="3">
+        <v>15.55176821474222</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.3408606731998295</v>
+      </c>
+      <c r="F6" s="3">
+        <v>15.2109075415424</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2528643140386811</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1830248516329766</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1698125474402299</v>
+      </c>
+      <c r="K6" s="4">
+        <v>76.74320090200538</v>
+      </c>
+      <c r="L6" s="4">
+        <v>74.81402790367821</v>
+      </c>
+      <c r="M6" s="5">
+        <v>2347</v>
+      </c>
+      <c r="N6" s="5">
+        <v>52611698.0483532</v>
+      </c>
+      <c r="O6" s="4">
+        <v>88.74159680525921</v>
+      </c>
+      <c r="P6" s="5">
+        <v>592864</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>98.66666666666667</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.08718548387245352</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.06723616703424461</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.05605621795225112</v>
+      </c>
+      <c r="K7" s="4">
+        <v>97.12071050642479</v>
+      </c>
+      <c r="L7" s="4">
+        <v>96.06390753168922</v>
+      </c>
+      <c r="M7" s="5">
+        <v>450</v>
+      </c>
+      <c r="N7" s="5">
+        <v>6814413.580417633</v>
+      </c>
+      <c r="O7" s="4">
+        <v>290.7421102661334</v>
+      </c>
+      <c r="P7" s="5">
+        <v>23438</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>98.12526629740094</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.8947592671495527</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.9799744354495101</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.3408606731998295</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.6391137622496805</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1172724290681785</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1006058510662128</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.0942604524042968</v>
+      </c>
+      <c r="K8" s="4">
+        <v>92.26870893223047</v>
+      </c>
+      <c r="L8" s="4">
+        <v>92.34699635595528</v>
+      </c>
+      <c r="M8" s="5">
+        <v>2347</v>
+      </c>
+      <c r="N8" s="5">
+        <v>26192348.20961952</v>
+      </c>
+      <c r="O8" s="4">
+        <v>146.8938477781116</v>
+      </c>
+      <c r="P8" s="5">
+        <v>178308</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1078,16 +2162,16 @@
         <v>1</v>
       </c>
       <c r="K4" s="5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -1122,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -1166,16 +2250,16 @@
         <v>2</v>
       </c>
       <c r="K6" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L6" s="5">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -1210,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
@@ -1254,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
         <v>0</v>
@@ -1279,9 +2363,368 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2298</v>
+      </c>
+      <c r="C3" s="5">
+        <v>25</v>
+      </c>
+      <c r="D3" s="5">
+        <v>24</v>
+      </c>
+      <c r="E3" s="5">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5">
+        <v>19</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2010</v>
+      </c>
+      <c r="C4" s="5">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5">
+        <v>326</v>
+      </c>
+      <c r="E4" s="5">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5">
+        <v>312</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>14</v>
+      </c>
+      <c r="I4" s="5">
+        <v>13</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5">
+        <v>293</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2305</v>
+      </c>
+      <c r="C5" s="5">
+        <v>21</v>
+      </c>
+      <c r="D5" s="5">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5">
+        <v>6</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1955</v>
+      </c>
+      <c r="C6" s="5">
+        <v>27</v>
+      </c>
+      <c r="D6" s="5">
+        <v>365</v>
+      </c>
+      <c r="E6" s="5">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5">
+        <v>357</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>8</v>
+      </c>
+      <c r="I6" s="5">
+        <v>6</v>
+      </c>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
+        <v>3</v>
+      </c>
+      <c r="L6" s="5">
+        <v>296</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>444</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2303</v>
+      </c>
+      <c r="C8" s="5">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5">
+        <v>8</v>
+      </c>
+      <c r="F8" s="5">
+        <v>15</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>8</v>
+      </c>
+      <c r="I8" s="5">
+        <v>8</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1292,9 +2735,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1328,8 +2777,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1351,10 +2808,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
         <v>0.2714054040849072</v>
@@ -1392,10 +2867,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2123151913397969</v>
+      </c>
+      <c r="O3" s="5">
+        <v>763</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1914368516891144</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1847242250111808</v>
+      </c>
+      <c r="R3" s="5">
+        <v>763</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
         <v>0.952379618446939</v>
@@ -1433,10 +2926,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.9535800996075487</v>
+      </c>
+      <c r="O4" s="5">
+        <v>382</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.095616022279224</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08569645927272489</v>
+      </c>
+      <c r="R4" s="5">
+        <v>382</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>0.8440680505180993</v>
@@ -1474,10 +2985,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.8491005216135552</v>
+      </c>
+      <c r="O5" s="5">
+        <v>367</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1976457159706748</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1957622352546503</v>
+      </c>
+      <c r="R5" s="5">
+        <v>367</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
         <v>0.3494389069572502</v>
@@ -1515,10 +3044,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.3428651775468071</v>
+      </c>
+      <c r="O6" s="5">
+        <v>366</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1291016511079466</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1291016511079466</v>
+      </c>
+      <c r="R6" s="5">
+        <v>366</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
         <v>0.3572628375220256</v>
@@ -1556,10 +3103,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.3515387497848434</v>
+      </c>
+      <c r="O7" s="5">
+        <v>355</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1155165817612965</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1116629485059709</v>
+      </c>
+      <c r="R7" s="5">
+        <v>355</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
         <v>1.415730506784846</v>
@@ -1597,10 +3162,26 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>4</v>
+      </c>
+      <c r="P8" s="4">
+        <v>1.415730506784846</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2449665764001594</v>
+      </c>
+      <c r="R8" s="5">
+        <v>4</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
         <v>0.8607194944851887</v>
@@ -1638,25 +3219,43 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-0.8607194944851887</v>
+      </c>
+      <c r="O9" s="5">
+        <v>23</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1118916344582952</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1118916344582952</v>
+      </c>
+      <c r="R9" s="5">
+        <v>23</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>0.304086867370188</v>
+        <v>0.1648133922629187</v>
       </c>
       <c r="C10" s="4">
-        <v>0.304086867370188</v>
+        <v>0.1648133922629187</v>
       </c>
       <c r="D10" s="4">
-        <v>0.05506962623174236</v>
+        <v>0.08966626541258979</v>
       </c>
       <c r="E10" s="4">
-        <v>95.75187969924814</v>
+        <v>97.19656283566053</v>
       </c>
       <c r="F10" s="4">
-        <v>85.67467326033207</v>
+        <v>96.14800423878508</v>
       </c>
       <c r="G10" s="5">
         <v>19</v>
@@ -1679,25 +3278,43 @@
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>-0.1648133922629187</v>
+      </c>
+      <c r="O10" s="5">
+        <v>19</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.08897560701588528</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.08897560701588528</v>
+      </c>
+      <c r="R10" s="5">
+        <v>19</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>0.1648133922629187</v>
+        <v>0.304086867370188</v>
       </c>
       <c r="C11" s="4">
-        <v>0.1648133922629187</v>
+        <v>0.304086867370188</v>
       </c>
       <c r="D11" s="4">
-        <v>0.08966626541258979</v>
+        <v>0.05506962623174236</v>
       </c>
       <c r="E11" s="4">
-        <v>97.19656283566053</v>
+        <v>95.75187969924814</v>
       </c>
       <c r="F11" s="4">
-        <v>96.14800423878508</v>
+        <v>85.67467326033207</v>
       </c>
       <c r="G11" s="5">
         <v>19</v>
@@ -1720,9 +3337,27 @@
       <c r="M11" s="5">
         <v>0</v>
       </c>
+      <c r="N11" s="4">
+        <v>-0.304086867370188</v>
+      </c>
+      <c r="O11" s="5">
+        <v>19</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.07741721094443595</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.07741721094443595</v>
+      </c>
+      <c r="R11" s="5">
+        <v>19</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1733,14 +3368,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1751,9 +3387,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1787,8 +3429,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1810,10 +3460,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
         <v>0.2747049298423114</v>
@@ -1851,10 +3519,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1485580440334285</v>
+      </c>
+      <c r="O3" s="5">
+        <v>662</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2493636142192992</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2156717196235757</v>
+      </c>
+      <c r="R3" s="5">
+        <v>662</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
         <v>0.3968253067302019</v>
@@ -1892,10 +3578,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3660851303865967</v>
+      </c>
+      <c r="O4" s="5">
+        <v>330</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.172518393442348</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1508205184154177</v>
+      </c>
+      <c r="R4" s="5">
+        <v>330</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>0.5585457507700523</v>
@@ -1933,10 +3637,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.5391769191970837</v>
+      </c>
+      <c r="O5" s="5">
+        <v>324</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2302504163088583</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.194372307144778</v>
+      </c>
+      <c r="R5" s="5">
+        <v>324</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
         <v>0.4841734964672755</v>
@@ -1974,10 +3696,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>0.4642952169109651</v>
+      </c>
+      <c r="O6" s="5">
+        <v>318</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1845448344623629</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1399538357415118</v>
+      </c>
+      <c r="R6" s="5">
+        <v>318</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
         <v>0.3023198918846033</v>
@@ -2015,10 +3755,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.1990965326205699</v>
+      </c>
+      <c r="O7" s="5">
+        <v>308</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2460843763865897</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1927427803232759</v>
+      </c>
+      <c r="R7" s="5">
+        <v>308</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
         <v>1.056736176736806</v>
@@ -2056,10 +3814,28 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.2988744455073444</v>
+      </c>
+      <c r="O8" s="5">
+        <v>8</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.7934839706848348</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1187699834667573</v>
+      </c>
+      <c r="R8" s="5">
+        <v>8</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
         <v>0.5898176901002108</v>
@@ -2097,40 +3873,58 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-0.5898176901002108</v>
+      </c>
+      <c r="O9" s="5">
+        <v>23</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1254977312677537</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1254977312677537</v>
+      </c>
+      <c r="R9" s="5">
+        <v>23</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>0.1355628969117608</v>
+        <v>0.1239682802316643</v>
       </c>
       <c r="C10" s="4">
-        <v>0.1395592208003885</v>
+        <v>0.1239682802316643</v>
       </c>
       <c r="D10" s="4">
-        <v>0.1871682236081705</v>
+        <v>0.08835500923107761</v>
       </c>
       <c r="E10" s="4">
-        <v>89.10669530970284</v>
+        <v>90.23451485857501</v>
       </c>
       <c r="F10" s="4">
-        <v>84.99352407865186</v>
+        <v>91.38702460850114</v>
       </c>
       <c r="G10" s="5">
         <v>19</v>
       </c>
       <c r="H10" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
       </c>
       <c r="J10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
         <v>0</v>
@@ -2138,40 +3932,58 @@
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>-0.1143242677640495</v>
+      </c>
+      <c r="O10" s="5">
+        <v>19</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1100043880114291</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1100043880114291</v>
+      </c>
+      <c r="R10" s="5">
+        <v>19</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>0.1239682802316643</v>
+        <v>0.1355628969117608</v>
       </c>
       <c r="C11" s="4">
-        <v>0.1239682802316643</v>
+        <v>0.1395592208003885</v>
       </c>
       <c r="D11" s="4">
-        <v>0.08835500923107761</v>
+        <v>0.1871682236081705</v>
       </c>
       <c r="E11" s="4">
-        <v>90.23451485857501</v>
+        <v>89.10669530970284</v>
       </c>
       <c r="F11" s="4">
-        <v>91.38702460850114</v>
+        <v>84.99352407865186</v>
       </c>
       <c r="G11" s="5">
         <v>19</v>
       </c>
       <c r="H11" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I11" s="5">
         <v>0</v>
       </c>
       <c r="J11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="5">
         <v>0</v>
@@ -2179,9 +3991,27 @@
       <c r="M11" s="5">
         <v>0</v>
       </c>
+      <c r="N11" s="4">
+        <v>0.04173661776221138</v>
+      </c>
+      <c r="O11" s="5">
+        <v>18</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.1337312952193934</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.1353071624716556</v>
+      </c>
+      <c r="R11" s="5">
+        <v>18</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2192,14 +4022,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2210,9 +4041,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -2246,8 +4083,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2269,10 +4114,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
         <v>0.2350494969065343</v>
@@ -2310,10 +4173,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1843564296198275</v>
+      </c>
+      <c r="O3" s="5">
+        <v>761</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1269080684527902</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1212253259283635</v>
+      </c>
+      <c r="R3" s="5">
+        <v>761</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
         <v>0.68986399042628</v>
@@ -2351,10 +4232,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.6918319271232417</v>
+      </c>
+      <c r="O4" s="5">
+        <v>385</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08408036902443702</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0825389904174882</v>
+      </c>
+      <c r="R4" s="5">
+        <v>385</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>0.7112990925645203</v>
@@ -2392,10 +4291,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.7051857787154489</v>
+      </c>
+      <c r="O5" s="5">
+        <v>372</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1295848053980439</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1286219572240791</v>
+      </c>
+      <c r="R5" s="5">
+        <v>372</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
         <v>0.3207411258816922</v>
@@ -2433,10 +4350,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.2737478315520311</v>
+      </c>
+      <c r="O6" s="5">
+        <v>366</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1181933749300087</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1181933749300087</v>
+      </c>
+      <c r="R6" s="5">
+        <v>366</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
         <v>0.6592109245410777</v>
@@ -2474,10 +4409,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.6616197947881672</v>
+      </c>
+      <c r="O7" s="5">
+        <v>356</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.10584850527163</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1033662020685157</v>
+      </c>
+      <c r="R7" s="5">
+        <v>356</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
         <v>1.05390733814769</v>
@@ -2515,10 +4468,28 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.3684333354968127</v>
+      </c>
+      <c r="O8" s="5">
+        <v>6</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.7075857312553897</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.08931036065411035</v>
+      </c>
+      <c r="R8" s="5">
+        <v>6</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
         <v>0.4777675398625572</v>
@@ -2556,91 +4527,145 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-0.4777675398625572</v>
+      </c>
+      <c r="O9" s="5">
+        <v>23</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1167222424808083</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1167222424808083</v>
+      </c>
+      <c r="R9" s="5">
+        <v>23</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>0.40929360711583</v>
+        <v>0.1977462462753579</v>
       </c>
       <c r="C10" s="4">
-        <v>0.40929360711583</v>
+        <v>0.1978690986155698</v>
       </c>
       <c r="D10" s="4">
-        <v>0.1492748427580122</v>
+        <v>0.1138390359582607</v>
       </c>
       <c r="E10" s="4">
-        <v>88.41031149301827</v>
+        <v>88.43537414965985</v>
       </c>
       <c r="F10" s="4">
-        <v>83.2014600259036</v>
+        <v>87.14058636524057</v>
       </c>
       <c r="G10" s="5">
         <v>19</v>
       </c>
       <c r="H10" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>-0.1978690986155698</v>
+      </c>
+      <c r="O10" s="5">
+        <v>17</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.0908918706712861</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1014397325692872</v>
+      </c>
+      <c r="R10" s="5">
+        <v>17</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>0.1977462462753579</v>
+        <v>0.40929360711583</v>
       </c>
       <c r="C11" s="4">
-        <v>0.1978690986155698</v>
+        <v>0.40929360711583</v>
       </c>
       <c r="D11" s="4">
-        <v>0.1138390359582607</v>
+        <v>0.1492748427580122</v>
       </c>
       <c r="E11" s="4">
-        <v>88.43537414965985</v>
+        <v>88.41031149301827</v>
       </c>
       <c r="F11" s="4">
-        <v>87.14058636524057</v>
+        <v>83.2014600259036</v>
       </c>
       <c r="G11" s="5">
         <v>19</v>
       </c>
       <c r="H11" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
+      <c r="N11" s="4">
+        <v>-0.40929360711583</v>
+      </c>
+      <c r="O11" s="5">
+        <v>19</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.09544489386197839</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.09544489386197839</v>
+      </c>
+      <c r="R11" s="5">
+        <v>19</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2651,14 +4676,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2669,9 +4695,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -2705,8 +4737,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2728,10 +4768,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
         <v>0.6089579992339776</v>
@@ -2769,10 +4827,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5427391400744215</v>
+      </c>
+      <c r="O3" s="5">
+        <v>627</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3110127047026556</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2460343259200287</v>
+      </c>
+      <c r="R3" s="5">
+        <v>627</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
         <v>0.5382421503420316</v>
@@ -2810,10 +4886,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4997808813135716</v>
+      </c>
+      <c r="O4" s="5">
+        <v>329</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1774084086067415</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1039484584563066</v>
+      </c>
+      <c r="R4" s="5">
+        <v>329</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>0.3480571024004803</v>
@@ -2851,10 +4945,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.1418049130595916</v>
+      </c>
+      <c r="O5" s="5">
+        <v>320</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2946436620928389</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2330059894413928</v>
+      </c>
+      <c r="R5" s="5">
+        <v>320</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
         <v>0.4998370639401143</v>
@@ -2892,10 +5004,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>0.4337319522795076</v>
+      </c>
+      <c r="O6" s="5">
+        <v>317</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2072226349566089</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.158711056942433</v>
+      </c>
+      <c r="R6" s="5">
+        <v>317</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
         <v>0.1893295328099953</v>
@@ -2933,10 +5063,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.06468327397395646</v>
+      </c>
+      <c r="O7" s="5">
+        <v>298</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1767078886068446</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1236674689927501</v>
+      </c>
+      <c r="R7" s="5">
+        <v>298</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
         <v>0.8874283462706738</v>
@@ -2974,10 +5122,28 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.06360884986328301</v>
+      </c>
+      <c r="O8" s="5">
+        <v>10</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.8372224251240736</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1623715557968672</v>
+      </c>
+      <c r="R8" s="5">
+        <v>10</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
         <v>0.1923978020599169</v>
@@ -3015,91 +5181,145 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-0.1923978020599169</v>
+      </c>
+      <c r="O9" s="5">
+        <v>23</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1276254083326428</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1276254083326428</v>
+      </c>
+      <c r="R9" s="5">
+        <v>23</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>0.5535181763172994</v>
+        <v>0.183057162141749</v>
       </c>
       <c r="C10" s="4">
-        <v>0.5535181763172994</v>
+        <v>0.07316644431803354</v>
       </c>
       <c r="D10" s="4">
-        <v>0.4150615305524968</v>
+        <v>0.06746074967247451</v>
       </c>
       <c r="E10" s="4">
-        <v>91.7901897601146</v>
+        <v>90.75725026852849</v>
       </c>
       <c r="F10" s="4">
-        <v>89.45013540562812</v>
+        <v>77.75403273283696</v>
       </c>
       <c r="G10" s="5">
         <v>19</v>
       </c>
       <c r="H10" s="5">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I10" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>-0.02319774828775678</v>
+      </c>
+      <c r="O10" s="5">
+        <v>12</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1836593130693184</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.08378557840658374</v>
+      </c>
+      <c r="R10" s="5">
+        <v>12</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>0.183057162141749</v>
+        <v>0.5535181763172994</v>
       </c>
       <c r="C11" s="4">
-        <v>0.07316644431803354</v>
+        <v>0.5535181763172994</v>
       </c>
       <c r="D11" s="4">
-        <v>0.06746074967247451</v>
+        <v>0.4150615305524968</v>
       </c>
       <c r="E11" s="4">
-        <v>90.75725026852849</v>
+        <v>91.7901897601146</v>
       </c>
       <c r="F11" s="4">
-        <v>77.75403273283696</v>
+        <v>89.45013540562812</v>
       </c>
       <c r="G11" s="5">
         <v>19</v>
       </c>
       <c r="H11" s="5">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
+      <c r="N11" s="4">
+        <v>-0.5535181763172994</v>
+      </c>
+      <c r="O11" s="5">
+        <v>19</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.1084350229553383</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.1084350229553383</v>
+      </c>
+      <c r="R11" s="5">
+        <v>19</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3110,14 +5330,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3128,9 +5349,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -3164,8 +5391,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3187,17 +5422,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
         <v>2.562563265448906</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>2.541576247187826</v>
       </c>
@@ -3228,10 +5479,28 @@
       <c r="M3" s="5">
         <v>153</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>2.562563265448906</v>
+      </c>
+      <c r="O3" s="5">
+        <v>153</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06820129169595052</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06820129169595052</v>
+      </c>
+      <c r="R3" s="5">
+        <v>153</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
         <v>1.390650125520955</v>
@@ -3269,17 +5538,33 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>1.390650125520955</v>
+      </c>
+      <c r="O4" s="5">
+        <v>71</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.041946941329485</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.041946941329485</v>
+      </c>
+      <c r="R4" s="5">
+        <v>71</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>4.60516113218758</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>4.585048442014883</v>
       </c>
@@ -3310,10 +5595,28 @@
       <c r="M5" s="5">
         <v>75</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>4.601236464865526</v>
+      </c>
+      <c r="O5" s="5">
+        <v>75</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06938913726083849</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06633732953796856</v>
+      </c>
+      <c r="R5" s="5">
+        <v>75</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
         <v>1.99825809103126</v>
@@ -3351,17 +5654,33 @@
       <c r="M6" s="5">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>1.99825809103126</v>
+      </c>
+      <c r="O6" s="5">
+        <v>74</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.0753605983711195</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.0753605983711195</v>
+      </c>
+      <c r="R6" s="5">
+        <v>74</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
         <v>3.849520267096413</v>
       </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="4">
         <v>3.816897438468335</v>
       </c>
@@ -3392,10 +5711,28 @@
       <c r="M7" s="5">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>3.83988001528099</v>
+      </c>
+      <c r="O7" s="5">
+        <v>65</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.07253836148883885</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.06386577289916089</v>
+      </c>
+      <c r="R7" s="5">
+        <v>65</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
         <v>1.717339340901367</v>
@@ -3433,10 +5770,26 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>1.717339340901367</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1406184614013455</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
         <v>0.3725695531657038</v>
@@ -3474,25 +5827,41 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>3</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.3725695531657038</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.3725695531657038</v>
+      </c>
+      <c r="R9" s="5">
+        <v>3</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>0.3135759248925183</v>
+        <v>0.1646654202838249</v>
       </c>
       <c r="C10" s="4">
-        <v>0.3135759248925183</v>
+        <v>0.1646654202838249</v>
       </c>
       <c r="D10" s="4">
-        <v>0.1305724992943738</v>
+        <v>0.1453337266345329</v>
       </c>
       <c r="E10" s="4">
-        <v>92.14285714285714</v>
+        <v>92.95918367346938</v>
       </c>
       <c r="F10" s="4">
-        <v>92.95302013422818</v>
+        <v>94.39597315436242</v>
       </c>
       <c r="G10" s="5">
         <v>1</v>
@@ -3515,25 +5884,41 @@
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4"/>
+      <c r="O10" s="5">
+        <v>1</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1646654202838249</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1646654202838249</v>
+      </c>
+      <c r="R10" s="5">
+        <v>1</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>0.1646654202838249</v>
+        <v>0.3135759248925183</v>
       </c>
       <c r="C11" s="4">
-        <v>0.1646654202838249</v>
+        <v>0.3135759248925183</v>
       </c>
       <c r="D11" s="4">
-        <v>0.1453337266345329</v>
+        <v>0.1305724992943738</v>
       </c>
       <c r="E11" s="4">
-        <v>92.95918367346938</v>
+        <v>92.14285714285714</v>
       </c>
       <c r="F11" s="4">
-        <v>94.39597315436242</v>
+        <v>92.95302013422818</v>
       </c>
       <c r="G11" s="5">
         <v>1</v>
@@ -3556,9 +5941,25 @@
       <c r="M11" s="5">
         <v>0</v>
       </c>
+      <c r="N11" s="4"/>
+      <c r="O11" s="5">
+        <v>1</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.3135759248925183</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.3135759248925183</v>
+      </c>
+      <c r="R11" s="5">
+        <v>1</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3569,465 +5970,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1208029301225156</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1164357392225056</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1008677856782264</v>
-      </c>
-      <c r="E3" s="4">
-        <v>93.33767361111113</v>
-      </c>
-      <c r="F3" s="4">
-        <v>93.10437639821068</v>
-      </c>
-      <c r="G3" s="5">
-        <v>768</v>
-      </c>
-      <c r="H3" s="5">
-        <v>762</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>6</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>6</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.6726984132912174</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6750157754981174</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.7014459875671282</v>
-      </c>
-      <c r="E4" s="4">
-        <v>89.2354409464044</v>
-      </c>
-      <c r="F4" s="4">
-        <v>91.12934926498252</v>
-      </c>
-      <c r="G4" s="5">
-        <v>387</v>
-      </c>
-      <c r="H4" s="5">
-        <v>384</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.743969930403469</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7470720611733199</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.7830508365590264</v>
-      </c>
-      <c r="E5" s="4">
-        <v>94.83978041618792</v>
-      </c>
-      <c r="F5" s="4">
-        <v>94.68215268906204</v>
-      </c>
-      <c r="G5" s="5">
-        <v>373</v>
-      </c>
-      <c r="H5" s="5">
-        <v>370</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.4001593216554759</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.4001593216554759</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.4312794525629082</v>
-      </c>
-      <c r="E6" s="4">
-        <v>94.36210549793688</v>
-      </c>
-      <c r="F6" s="4">
-        <v>94.49636923753988</v>
-      </c>
-      <c r="G6" s="5">
-        <v>366</v>
-      </c>
-      <c r="H6" s="5">
-        <v>366</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.6602296127143477</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.6632745647065104</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.6900633889062732</v>
-      </c>
-      <c r="E7" s="4">
-        <v>89.95468019610078</v>
-      </c>
-      <c r="F7" s="4">
-        <v>91.34824965942781</v>
-      </c>
-      <c r="G7" s="5">
-        <v>358</v>
-      </c>
-      <c r="H7" s="5">
-        <v>355</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>3</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>3</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1.233992995803142</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.1693688893909946</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.0818765785737585</v>
-      </c>
-      <c r="E8" s="4">
-        <v>85.03401360544217</v>
-      </c>
-      <c r="F8" s="4">
-        <v>55.56224503224157</v>
-      </c>
-      <c r="G8" s="5">
-        <v>34</v>
-      </c>
-      <c r="H8" s="5">
-        <v>5</v>
-      </c>
-      <c r="I8" s="5">
-        <v>21</v>
-      </c>
-      <c r="J8" s="5">
-        <v>8</v>
-      </c>
-      <c r="K8" s="5">
-        <v>8</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4">
-        <v>0.5273506053844588</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0.5273506053844588</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.3549032685483309</v>
-      </c>
-      <c r="E9" s="4">
-        <v>87.90594498669033</v>
-      </c>
-      <c r="F9" s="4">
-        <v>90.44013228285158</v>
-      </c>
-      <c r="G9" s="5">
-        <v>23</v>
-      </c>
-      <c r="H9" s="5">
-        <v>23</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0.7082824204476088</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0.7082824204476088</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0.4929906137282688</v>
-      </c>
-      <c r="E10" s="4">
-        <v>86.96025778732547</v>
-      </c>
-      <c r="F10" s="4">
-        <v>88.50582832921232</v>
-      </c>
-      <c r="G10" s="5">
-        <v>19</v>
-      </c>
-      <c r="H10" s="5">
-        <v>19</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0.1069924771169251</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0.1069924771169251</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.0293032420202812</v>
-      </c>
-      <c r="E11" s="4">
-        <v>87.18045112781958</v>
-      </c>
-      <c r="F11" s="4">
-        <v>90.08124337689878</v>
-      </c>
-      <c r="G11" s="5">
-        <v>19</v>
-      </c>
-      <c r="H11" s="5">
-        <v>19</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/Sainifirst2023.xlsx
+++ b/public/downloads/Sainifirst2023.xlsx
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.04944611452185842</v>
+        <v>0.02848159305028197</v>
       </c>
       <c r="O3" s="5">
         <v>762</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1191112156310864</v>
+        <v>0.1179928747361111</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1151200436289538</v>
+        <v>0.1138278219279426</v>
       </c>
       <c r="R3" s="5">
         <v>762</v>
@@ -1148,16 +1148,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6750157754981174</v>
+        <v>-0.6923881158538645</v>
       </c>
       <c r="O4" s="5">
         <v>384</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07133916625296793</v>
+        <v>0.06960495818518993</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06956103689017767</v>
+        <v>0.06767755891284087</v>
       </c>
       <c r="R4" s="5">
         <v>384</v>
@@ -1207,16 +1207,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7470720611733199</v>
+        <v>-0.7385330252246516</v>
       </c>
       <c r="O5" s="5">
         <v>370</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1174712148105223</v>
+        <v>0.117238332940585</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1152964009382985</v>
+        <v>0.1151308662635941</v>
       </c>
       <c r="R5" s="5">
         <v>370</v>
@@ -1266,16 +1266,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.3985188860917027</v>
+        <v>-0.408516812181003</v>
       </c>
       <c r="O6" s="5">
         <v>366</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1039660288404617</v>
+        <v>0.1036601001465106</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1039660288404617</v>
+        <v>0.1036601001465106</v>
       </c>
       <c r="R6" s="5">
         <v>366</v>
@@ -1325,16 +1325,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.6632745647065104</v>
+        <v>-0.6805541468976788</v>
       </c>
       <c r="O7" s="5">
         <v>355</v>
       </c>
       <c r="P7" s="4">
-        <v>0.08896950673792484</v>
+        <v>0.08782246698329345</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.08605916275446153</v>
+        <v>0.08475640506789379</v>
       </c>
       <c r="R7" s="5">
         <v>355</v>
@@ -1384,16 +1384,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1693688893909946</v>
+        <v>-0.1913752419720822</v>
       </c>
       <c r="O8" s="5">
         <v>5</v>
       </c>
       <c r="P8" s="4">
-        <v>1.080621056438547</v>
+        <v>1.062826478723663</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.06158696927266263</v>
+        <v>0.05061560371688687</v>
       </c>
       <c r="R8" s="5">
         <v>5</v>
@@ -1443,16 +1443,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5273506053844588</v>
+        <v>-0.4792979964994473</v>
       </c>
       <c r="O9" s="5">
         <v>23</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1176321160800899</v>
+        <v>0.09697833889189365</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1176321160800899</v>
+        <v>0.09697833889189365</v>
       </c>
       <c r="R9" s="5">
         <v>23</v>
@@ -1502,16 +1502,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1069924771169251</v>
+        <v>-0.05474746930980245</v>
       </c>
       <c r="O10" s="5">
         <v>19</v>
       </c>
       <c r="P10" s="4">
-        <v>0.08782386185518783</v>
+        <v>0.06502782362998598</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.08782386185518783</v>
+        <v>0.06502782362998598</v>
       </c>
       <c r="R10" s="5">
         <v>19</v>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.7082824204476088</v>
+        <v>-0.6893468497170785</v>
       </c>
       <c r="O11" s="5">
         <v>19</v>
       </c>
       <c r="P11" s="4">
-        <v>0.06936836959631029</v>
+        <v>0.06536237782424061</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.06936836959631029</v>
+        <v>0.06536237782424061</v>
       </c>
       <c r="R11" s="5">
         <v>19</v>
@@ -1707,13 +1707,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.1705260774251749</v>
+        <v>0.1700733447302849</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1475769190290183</v>
+        <v>0.1470688876853937</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1477748018957475</v>
+        <v>0.1462017273483915</v>
       </c>
       <c r="K3" s="4">
         <v>93.53269045155318</v>
@@ -1757,13 +1757,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2276509485425082</v>
+        <v>0.2270869991787034</v>
       </c>
       <c r="I4" s="4">
-        <v>0.182962384612822</v>
+        <v>0.1826886998529136</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2132956707178462</v>
+        <v>0.2121985606161267</v>
       </c>
       <c r="K4" s="4">
         <v>84.52786738896678</v>
@@ -1807,13 +1807,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1234661682467707</v>
+        <v>0.120077910320532</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1122311920904071</v>
+        <v>0.1087146749656852</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1021687578544897</v>
+        <v>0.09435890144749452</v>
       </c>
       <c r="K5" s="4">
         <v>93.92240492277006</v>
@@ -1857,13 +1857,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2528643140386811</v>
+        <v>0.2501464378494666</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1830248516329766</v>
+        <v>0.1804701017951387</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1698125474402299</v>
+        <v>0.1714481641540094</v>
       </c>
       <c r="K6" s="4">
         <v>76.74320090200538</v>
@@ -1907,13 +1907,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.08718548387245352</v>
+        <v>0.08500411631900767</v>
       </c>
       <c r="I7" s="4">
-        <v>0.06723616703424461</v>
+        <v>0.06493970007913386</v>
       </c>
       <c r="J7" s="4">
-        <v>0.05605621795225112</v>
+        <v>0.05233934624371216</v>
       </c>
       <c r="K7" s="4">
         <v>97.12071050642479</v>
@@ -1957,13 +1957,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1172724290681785</v>
+        <v>0.1156836815228932</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1006058510662128</v>
+        <v>0.09913700284090597</v>
       </c>
       <c r="J8" s="4">
-        <v>0.0942604524042968</v>
+        <v>0.09111497920621836</v>
       </c>
       <c r="K8" s="4">
         <v>92.26870893223047</v>
@@ -2868,16 +2868,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2123151913397969</v>
+        <v>-0.2247206213323807</v>
       </c>
       <c r="O3" s="5">
         <v>763</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1914368516891144</v>
+        <v>0.191236682651319</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1847242250111808</v>
+        <v>0.1844414504751522</v>
       </c>
       <c r="R3" s="5">
         <v>763</v>
@@ -2927,16 +2927,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.9535800996075487</v>
+        <v>-0.9546449713818106</v>
       </c>
       <c r="O4" s="5">
         <v>382</v>
       </c>
       <c r="P4" s="4">
-        <v>0.095616022279224</v>
+        <v>0.09562872271852713</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08569645927272489</v>
+        <v>0.085695387835916</v>
       </c>
       <c r="R4" s="5">
         <v>382</v>
@@ -2986,16 +2986,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.8491005216135552</v>
+        <v>-0.8522582697888197</v>
       </c>
       <c r="O5" s="5">
         <v>367</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1976457159706748</v>
+        <v>0.1976811372610243</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1957622352546503</v>
+        <v>0.1957466103288976</v>
       </c>
       <c r="R5" s="5">
         <v>367</v>
@@ -3045,16 +3045,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.3428651775468071</v>
+        <v>-0.3489747234650054</v>
       </c>
       <c r="O6" s="5">
         <v>366</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1291016511079466</v>
+        <v>0.1290291203834708</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1291016511079466</v>
+        <v>0.1290291203834708</v>
       </c>
       <c r="R6" s="5">
         <v>366</v>
@@ -3104,16 +3104,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3515387497848434</v>
+        <v>-0.3577368814037527</v>
       </c>
       <c r="O7" s="5">
         <v>355</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1155165817612965</v>
+        <v>0.1154970122949801</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1116629485059709</v>
+        <v>0.1115908350868217</v>
       </c>
       <c r="R7" s="5">
         <v>355</v>
@@ -3220,16 +3220,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.8607194944851887</v>
+        <v>-0.7945166024267678</v>
       </c>
       <c r="O9" s="5">
         <v>23</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1118916344582952</v>
+        <v>0.09285314085598351</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1118916344582952</v>
+        <v>0.09285314085598351</v>
       </c>
       <c r="R9" s="5">
         <v>23</v>
@@ -3279,16 +3279,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1648133922629187</v>
+        <v>-0.1167162972485016</v>
       </c>
       <c r="O10" s="5">
         <v>19</v>
       </c>
       <c r="P10" s="4">
-        <v>0.08897560701588528</v>
+        <v>0.06697716608347323</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.08897560701588528</v>
+        <v>0.06697716608347323</v>
       </c>
       <c r="R10" s="5">
         <v>19</v>
@@ -3338,16 +3338,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.304086867370188</v>
+        <v>-0.29188903396971</v>
       </c>
       <c r="O11" s="5">
         <v>19</v>
       </c>
       <c r="P11" s="4">
-        <v>0.07741721094443595</v>
+        <v>0.07544072775905725</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.07741721094443595</v>
+        <v>0.07544072775905725</v>
       </c>
       <c r="R11" s="5">
         <v>19</v>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1485580440334285</v>
+        <v>0.1439213635681256</v>
       </c>
       <c r="O3" s="5">
         <v>662</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2493636142192992</v>
+        <v>0.2492069687543027</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2156717196235757</v>
+        <v>0.2156300812401175</v>
       </c>
       <c r="R3" s="5">
         <v>662</v>
@@ -3579,16 +3579,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3660851303865967</v>
+        <v>-0.3767423464111346</v>
       </c>
       <c r="O4" s="5">
         <v>330</v>
       </c>
       <c r="P4" s="4">
-        <v>0.172518393442348</v>
+        <v>0.1721700298220609</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1508205184154177</v>
+        <v>0.1506380450551773</v>
       </c>
       <c r="R4" s="5">
         <v>330</v>
@@ -3638,16 +3638,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5391769191970837</v>
+        <v>-0.5385393061089871</v>
       </c>
       <c r="O5" s="5">
         <v>324</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2302504163088583</v>
+        <v>0.2302364669515868</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.194372307144778</v>
+        <v>0.1943700237538965</v>
       </c>
       <c r="R5" s="5">
         <v>324</v>
@@ -3697,16 +3697,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.4642952169109651</v>
+        <v>0.4571018330858863</v>
       </c>
       <c r="O6" s="5">
         <v>318</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1845448344623629</v>
+        <v>0.1842341814929093</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1399538357415118</v>
+        <v>0.1398677402040305</v>
       </c>
       <c r="R6" s="5">
         <v>318</v>
@@ -3756,16 +3756,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1990965326205699</v>
+        <v>-0.2099791087634628</v>
       </c>
       <c r="O7" s="5">
         <v>308</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2460843763865897</v>
+        <v>0.2459255834368936</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1927427803232759</v>
+        <v>0.1926288753761804</v>
       </c>
       <c r="R7" s="5">
         <v>308</v>
@@ -3815,16 +3815,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2988744455073444</v>
+        <v>-0.3262791806237715</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.7934839706848348</v>
+        <v>0.7780340893387762</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1187699834667573</v>
+        <v>0.1147686417579692</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5898176901002108</v>
+        <v>-0.5463351453125256</v>
       </c>
       <c r="O9" s="5">
         <v>23</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1254977312677537</v>
+        <v>0.1182542515446649</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1254977312677537</v>
+        <v>0.1182542515446649</v>
       </c>
       <c r="R9" s="5">
         <v>23</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1143242677640495</v>
+        <v>-0.06169882593502507</v>
       </c>
       <c r="O10" s="5">
         <v>19</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1100043880114291</v>
+        <v>0.09945102705797269</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1100043880114291</v>
+        <v>0.09945102705797269</v>
       </c>
       <c r="R10" s="5">
         <v>19</v>
@@ -3992,13 +3992,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.04173661776221138</v>
+        <v>0.04142772966679331</v>
       </c>
       <c r="O11" s="5">
         <v>18</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1337312952193934</v>
+        <v>0.1337150379512135</v>
       </c>
       <c r="Q11" s="4">
         <v>0.1353071624716556</v>
@@ -4174,16 +4174,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1843564296198275</v>
+        <v>-0.2071139241794526</v>
       </c>
       <c r="O3" s="5">
         <v>761</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1269080684527902</v>
+        <v>0.1250498090335039</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1212253259283635</v>
+        <v>0.1191406403883776</v>
       </c>
       <c r="R3" s="5">
         <v>761</v>
@@ -4233,16 +4233,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6918319271232417</v>
+        <v>-0.717325101481606</v>
       </c>
       <c r="O4" s="5">
         <v>385</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08408036902443702</v>
+        <v>0.0814585691395625</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0825389904174882</v>
+        <v>0.07977113871836307</v>
       </c>
       <c r="R4" s="5">
         <v>385</v>
@@ -4292,16 +4292,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7051857787154489</v>
+        <v>-0.7368934459625791</v>
       </c>
       <c r="O5" s="5">
         <v>372</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1295848053980439</v>
+        <v>0.1256726782579327</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1286219572240791</v>
+        <v>0.1246140779485183</v>
       </c>
       <c r="R5" s="5">
         <v>372</v>
@@ -4351,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.2737478315520311</v>
+        <v>-0.3061750408285207</v>
       </c>
       <c r="O6" s="5">
         <v>366</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1181933749300087</v>
+        <v>0.1131842061132582</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1181933749300087</v>
+        <v>0.1131842061132582</v>
       </c>
       <c r="R6" s="5">
         <v>366</v>
@@ -4410,16 +4410,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.6616197947881672</v>
+        <v>-0.6899424190430352</v>
       </c>
       <c r="O7" s="5">
         <v>356</v>
       </c>
       <c r="P7" s="4">
-        <v>0.10584850527163</v>
+        <v>0.1028090807518718</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1033662020685157</v>
+        <v>0.1001505862635068</v>
       </c>
       <c r="R7" s="5">
         <v>356</v>
@@ -4469,13 +4469,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.3684333354968127</v>
+        <v>-0.3783354743790994</v>
       </c>
       <c r="O8" s="5">
         <v>6</v>
       </c>
       <c r="P8" s="4">
-        <v>0.7075857312553897</v>
+        <v>0.7000135074042295</v>
       </c>
       <c r="Q8" s="4">
         <v>0.08931036065411035</v>
@@ -4528,16 +4528,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4777675398625572</v>
+        <v>-0.4209263717109479</v>
       </c>
       <c r="O9" s="5">
         <v>23</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1167222424808083</v>
+        <v>0.09323280698650586</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1167222424808083</v>
+        <v>0.09323280698650586</v>
       </c>
       <c r="R9" s="5">
         <v>23</v>
@@ -4587,16 +4587,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1978690986155698</v>
+        <v>-0.1393947047700976</v>
       </c>
       <c r="O10" s="5">
         <v>17</v>
       </c>
       <c r="P10" s="4">
-        <v>0.0908918706712861</v>
+        <v>0.07366449599723673</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1014397325692872</v>
+        <v>0.07558887239532824</v>
       </c>
       <c r="R10" s="5">
         <v>17</v>
@@ -4646,16 +4646,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.40929360711583</v>
+        <v>-0.4045579780727735</v>
       </c>
       <c r="O11" s="5">
         <v>19</v>
       </c>
       <c r="P11" s="4">
-        <v>0.09544489386197839</v>
+        <v>0.09519565022813331</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.09544489386197839</v>
+        <v>0.09519565022813331</v>
       </c>
       <c r="R11" s="5">
         <v>19</v>
@@ -4828,16 +4828,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5427391400744215</v>
+        <v>0.5586505897290408</v>
       </c>
       <c r="O3" s="5">
         <v>627</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3110127047026556</v>
+        <v>0.3105297985474638</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2460343259200287</v>
+        <v>0.2455957095225277</v>
       </c>
       <c r="R3" s="5">
         <v>627</v>
@@ -4887,16 +4887,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4997808813135716</v>
+        <v>-0.5211409943121339</v>
       </c>
       <c r="O4" s="5">
         <v>329</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1774084086067415</v>
+        <v>0.1769324202648595</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1039484584563066</v>
+        <v>0.1024608757545374</v>
       </c>
       <c r="R4" s="5">
         <v>329</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1418049130595916</v>
+        <v>0.2128554676648378</v>
       </c>
       <c r="O5" s="5">
         <v>320</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2946436620928389</v>
+        <v>0.2859413529970304</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2330059894413928</v>
+        <v>0.2265557757380419</v>
       </c>
       <c r="R5" s="5">
         <v>320</v>
@@ -5005,16 +5005,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.4337319522795076</v>
+        <v>0.4691672761865675</v>
       </c>
       <c r="O6" s="5">
         <v>317</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2072226349566089</v>
+        <v>0.2031304727535814</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.158711056942433</v>
+        <v>0.1549152627057825</v>
       </c>
       <c r="R6" s="5">
         <v>317</v>
@@ -5064,16 +5064,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.06468327397395646</v>
+        <v>-0.08688151551021406</v>
       </c>
       <c r="O7" s="5">
         <v>298</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1767078886068446</v>
+        <v>0.1768335401641147</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1236674689927501</v>
+        <v>0.1219988777574565</v>
       </c>
       <c r="R7" s="5">
         <v>298</v>
@@ -5123,16 +5123,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.06360884986328301</v>
+        <v>-0.0985436871289096</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
       </c>
       <c r="P8" s="4">
-        <v>0.8372224251240736</v>
+        <v>0.8123232646783031</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1623715557968672</v>
+        <v>0.157698570109369</v>
       </c>
       <c r="R8" s="5">
         <v>10</v>
@@ -5182,16 +5182,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.1923978020599169</v>
+        <v>-0.1343908700048928</v>
       </c>
       <c r="O9" s="5">
         <v>23</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1276254083326428</v>
+        <v>0.115824242068611</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1276254083326428</v>
+        <v>0.115824242068611</v>
       </c>
       <c r="R9" s="5">
         <v>23</v>
@@ -5241,16 +5241,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.02319774828775678</v>
+        <v>0.004863930888689083</v>
       </c>
       <c r="O10" s="5">
         <v>12</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1836593130693184</v>
+        <v>0.184122987804274</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.08378557840658374</v>
+        <v>0.07282736374674433</v>
       </c>
       <c r="R10" s="5">
         <v>12</v>
@@ -5300,16 +5300,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.5535181763172994</v>
+        <v>-0.5376400365331619</v>
       </c>
       <c r="O11" s="5">
         <v>19</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1084350229553383</v>
+        <v>0.1075993313877521</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1084350229553383</v>
+        <v>0.1075993313877521</v>
       </c>
       <c r="R11" s="5">
         <v>19</v>
@@ -5480,16 +5480,16 @@
         <v>153</v>
       </c>
       <c r="N3" s="4">
-        <v>2.562563265448906</v>
+        <v>2.54815538885498</v>
       </c>
       <c r="O3" s="5">
         <v>153</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06820129169595052</v>
+        <v>0.06684311083767058</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06820129169595052</v>
+        <v>0.06684311083767058</v>
       </c>
       <c r="R3" s="5">
         <v>153</v>
@@ -5539,16 +5539,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>1.390650125520955</v>
+        <v>1.382667530356457</v>
       </c>
       <c r="O4" s="5">
         <v>71</v>
       </c>
       <c r="P4" s="4">
-        <v>0.041946941329485</v>
+        <v>0.04165268675340543</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.041946941329485</v>
+        <v>0.04165268675340543</v>
       </c>
       <c r="R4" s="5">
         <v>71</v>
@@ -5596,16 +5596,16 @@
         <v>75</v>
       </c>
       <c r="N5" s="4">
-        <v>4.601236464865526</v>
+        <v>4.578456784779064</v>
       </c>
       <c r="O5" s="5">
         <v>75</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06938913726083849</v>
+        <v>0.06625043829871508</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06633732953796856</v>
+        <v>0.06285305218853068</v>
       </c>
       <c r="R5" s="5">
         <v>75</v>
@@ -5655,16 +5655,16 @@
         <v>23</v>
       </c>
       <c r="N6" s="4">
-        <v>1.99825809103126</v>
+        <v>1.968928487100243</v>
       </c>
       <c r="O6" s="5">
         <v>74</v>
       </c>
       <c r="P6" s="4">
-        <v>0.0753605983711195</v>
+        <v>0.07056183390783363</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.0753605983711195</v>
+        <v>0.07056183390783363</v>
       </c>
       <c r="R6" s="5">
         <v>74</v>
@@ -5712,16 +5712,16 @@
         <v>65</v>
       </c>
       <c r="N7" s="4">
-        <v>3.83988001528099</v>
+        <v>3.824643766348913</v>
       </c>
       <c r="O7" s="5">
         <v>65</v>
       </c>
       <c r="P7" s="4">
-        <v>0.07253836148883885</v>
+        <v>0.07012514995205672</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.06386577289916089</v>
+        <v>0.06118103120131939</v>
       </c>
       <c r="R7" s="5">
         <v>65</v>
